--- a/temporario/Apontamento_Daves.xlsx
+++ b/temporario/Apontamento_Daves.xlsx
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="M2" s="75" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="N2" s="37" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="Q2" s="76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Permaco</t>
         </is>
       </c>
       <c r="R2" s="26" t="n"/>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="4">
       <c r="A4" s="80" t="n">
-        <v>0</v>
+        <v>21593</v>
       </c>
       <c r="B4" s="81" t="inlineStr">
         <is>
-          <t>26/02257</t>
+          <t>26/02225</t>
         </is>
       </c>
       <c r="C4" s="82" t="inlineStr">
         <is>
-          <t>ALFA TRANSPORTES</t>
+          <t>PLASTIMIL</t>
         </is>
       </c>
       <c r="D4" s="83" t="n"/>
       <c r="E4" s="82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17000 x 1700 x 100</t>
         </is>
       </c>
       <c r="F4" s="83" t="n"/>
@@ -1513,25 +1513,23 @@
       <c r="S4" s="18" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="86" t="inlineStr">
-        <is>
-          <t>FAT27841584</t>
-        </is>
+      <c r="A5" s="86" t="n">
+        <v>0</v>
       </c>
       <c r="B5" s="87" t="inlineStr">
         <is>
-          <t>26/02258</t>
+          <t>26/02345</t>
         </is>
       </c>
       <c r="C5" s="76" t="inlineStr">
         <is>
-          <t>CASA MAIS</t>
+          <t>FRUTTY</t>
         </is>
       </c>
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="76" t="inlineStr">
         <is>
-          <t>4,5 + 0,5</t>
+          <t>60 + 350</t>
         </is>
       </c>
       <c r="F5" s="26" t="n"/>
@@ -1552,23 +1550,23 @@
     <row r="6">
       <c r="A6" s="86" t="inlineStr">
         <is>
-          <t>FAT25708839</t>
+          <t>FAT25732698</t>
         </is>
       </c>
       <c r="B6" s="87" t="inlineStr">
         <is>
-          <t>26/02263</t>
+          <t>26/01929</t>
         </is>
       </c>
       <c r="C6" s="76" t="inlineStr">
         <is>
-          <t>GL FOODS</t>
+          <t>I&amp;M</t>
         </is>
       </c>
       <c r="D6" s="26" t="n"/>
       <c r="E6" s="76" t="inlineStr">
         <is>
-          <t>3 + 0,5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F6" s="26" t="n"/>

--- a/temporario/Apontamento_Daves.xlsx
+++ b/temporario/Apontamento_Daves.xlsx
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="M2" s="75" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="N2" s="37" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="Q2" s="76" t="inlineStr">
         <is>
-          <t>Permaco</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R2" s="26" t="n"/>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="4">
       <c r="A4" s="80" t="n">
-        <v>21593</v>
+        <v>0</v>
       </c>
       <c r="B4" s="81" t="inlineStr">
         <is>
-          <t>26/02225</t>
+          <t>26/02257</t>
         </is>
       </c>
       <c r="C4" s="82" t="inlineStr">
         <is>
-          <t>PLASTIMIL</t>
+          <t>ALFA TRANSPORTES</t>
         </is>
       </c>
       <c r="D4" s="83" t="n"/>
       <c r="E4" s="82" t="inlineStr">
         <is>
-          <t>17000 x 1700 x 100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" s="83" t="n"/>
@@ -1513,23 +1513,25 @@
       <c r="S4" s="18" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="86" t="n">
-        <v>0</v>
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t>FAT27841584</t>
+        </is>
       </c>
       <c r="B5" s="87" t="inlineStr">
         <is>
-          <t>26/02345</t>
+          <t>26/02258</t>
         </is>
       </c>
       <c r="C5" s="76" t="inlineStr">
         <is>
-          <t>FRUTTY</t>
+          <t>CASA MAIS</t>
         </is>
       </c>
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="76" t="inlineStr">
         <is>
-          <t>60 + 350</t>
+          <t>4,5 + 0,5</t>
         </is>
       </c>
       <c r="F5" s="26" t="n"/>
@@ -1550,23 +1552,23 @@
     <row r="6">
       <c r="A6" s="86" t="inlineStr">
         <is>
-          <t>FAT25732698</t>
+          <t>FAT25708839</t>
         </is>
       </c>
       <c r="B6" s="87" t="inlineStr">
         <is>
-          <t>26/01929</t>
+          <t>26/02263</t>
         </is>
       </c>
       <c r="C6" s="76" t="inlineStr">
         <is>
-          <t>I&amp;M</t>
+          <t>GL FOODS</t>
         </is>
       </c>
       <c r="D6" s="26" t="n"/>
       <c r="E6" s="76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3 + 0,5</t>
         </is>
       </c>
       <c r="F6" s="26" t="n"/>
